--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Tessera elettorale.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Tessera elettorale.xlsx
@@ -370,7 +370,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
+      <t xml:space="preserve">.
 Per ulteriori informazioni, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -443,7 +443,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> è stata rilasciata una tessera elettorale a tuo nome. È stata inviata per posta al tuo indirizzo di residenza. 
+      <t xml:space="preserve"> è stata rilasciata una tessera elettorale a tuo nome. È stata inviata per posta al tuo indirizzo di residenza.
 Per ulteriori informazioni, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -481,7 +481,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
